--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484534_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484534_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>J. CONDE BARBERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6349</v>
+        <v>0.4773</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.676</v>
+        <v>-0.5615</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3109</v>
+        <v>1.0388</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2362</v>
+        <v>0.835</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.1655</v>
+        <v>1.2839</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9293</v>
+        <v>-0.4489</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.0252</v>
+        <v>0.3468</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.8587</v>
+        <v>0.3468</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8335</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.211</v>
+        <v>0.4882</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3068</v>
+        <v>0.9371</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0958</v>
+        <v>-0.4489</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.8484</v>
+        <v>-0.1833</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7489</v>
+        <v>0.3665</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8136</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6637</v>
+        <v>0.5211</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1499</v>
+        <v>0.184</v>
       </c>
       <c r="V2" t="n">
-        <v>3.157</v>
+        <v>-1.2461</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5339</v>
+        <v>-1.2461</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CONDE BARBERA</t>
+          <t>A. BALADA SEGOVIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1856</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.345</v>
+        <v>1.8555</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8406</v>
+        <v>-1.7782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.835</v>
+        <v>-0.2037</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2839</v>
+        <v>0.5977</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4489</v>
+        <v>-0.8014</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3468</v>
+        <v>0.201</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3468</v>
+        <v>1.4831</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.2821</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4882</v>
+        <v>-0.4047</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9371</v>
+        <v>-0.8854</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4489</v>
+        <v>0.4807</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4134</v>
+        <v>-0.096</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4276</v>
+        <v>0.0264</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0142</v>
+        <v>-0.1224</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2461</v>
+        <v>0.0104</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.2461</v>
+        <v>2.5444</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BALADA SEGOVIA</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6345</v>
+        <v>-0.1684</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1684</v>
+        <v>-1.7608</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.803</v>
+        <v>1.5924</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2037</v>
+        <v>-2.2362</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5977</v>
+        <v>-3.1655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8014</v>
+        <v>0.9293</v>
       </c>
       <c r="J4" t="n">
-        <v>0.201</v>
+        <v>-1.0252</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4831</v>
+        <v>-1.8587</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2821</v>
+        <v>0.8335</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4047</v>
+        <v>-1.211</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8854</v>
+        <v>-1.3068</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4807</v>
+        <v>0.0958</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3665</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>-3.8484</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2828</v>
+        <v>2.7489</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8078</v>
+        <v>0.0104</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6606</v>
+        <v>0.5788</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1471</v>
+        <v>-0.5685</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0104</v>
+        <v>3.157</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5444</v>
+        <v>2.5339</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.5339</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CARRERAS GARRIGA</t>
+          <t>J. TALLON GUIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7846</v>
+        <v>-0.3478</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6874</v>
+        <v>-0.1693</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1784</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3505</v>
+        <v>-0.4249</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6069</v>
+        <v>-0.7678</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2564</v>
+        <v>0.3429</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5977</v>
+        <v>0.0516</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5977</v>
+        <v>-0.0992</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.1508</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2472</v>
+        <v>-0.4765</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0092</v>
+        <v>-0.6686</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2564</v>
+        <v>0.1922</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1959</v>
+        <v>-0.9387</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4404</v>
+        <v>-0.221</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2446</v>
+        <v>-0.7178</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3115</v>
+        <v>-0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9554</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TALLON GUIA</t>
+          <t>J. CARRERAS GARRIGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9058</v>
+        <v>-0.5154</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.554</v>
+        <v>-0.3439</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3518</v>
+        <v>-0.1715</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4249</v>
+        <v>-0.3505</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7678</v>
+        <v>-0.6069</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3429</v>
+        <v>0.2564</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0516</v>
+        <v>-0.5977</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0992</v>
+        <v>-0.5977</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1508</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4765</v>
+        <v>0.2472</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6686</v>
+        <v>-0.0092</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1922</v>
+        <v>0.2564</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6493</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4968</v>
+        <v>0.0733</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6056</v>
+        <v>-0.0969</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8912</v>
+        <v>0.1702</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6335</v>
+        <v>0.3115</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6335</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0961</v>
+        <v>-1.2758</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.02</v>
+        <v>-0.1951</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0761</v>
+        <v>-1.0806</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3531</v>
+        <v>0.3078</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1088</v>
+        <v>-1.6252</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4619</v>
+        <v>1.9329</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1732</v>
+        <v>0.8085</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7369</v>
+        <v>-0.4834</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5637</v>
+        <v>1.2919</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1799</v>
+        <v>-0.5008</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8457</v>
+        <v>-1.1418</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0256</v>
+        <v>0.641</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0901</v>
+        <v>0.618</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2625</v>
+        <v>0.5253</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1723</v>
+        <v>0.0927</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2566</v>
+        <v>-2.2016</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6231</v>
+        <v>-0.6127</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6335</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2897</v>
+        <v>-1.2761</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2091</v>
+        <v>-0.8146</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0806</v>
+        <v>-0.4615</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3078</v>
+        <v>-3.4371</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6252</v>
+        <v>-3.2096</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9329</v>
+        <v>-0.2275</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8085</v>
+        <v>-1.7317</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4834</v>
+        <v>-2.4341</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2919</v>
+        <v>0.7024</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5008</v>
+        <v>-1.7054</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1418</v>
+        <v>-0.7756</v>
       </c>
       <c r="O8" t="n">
-        <v>0.641</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6041</v>
+        <v>-1.0119</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5113</v>
+        <v>-0.1666</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0927</v>
+        <v>-0.8452</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2016</v>
+        <v>1.89</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6127</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5889</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3839</v>
+        <v>-1.8241</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.749</v>
+        <v>-1.6241</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6349</v>
+        <v>-0.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4371</v>
+        <v>0.3531</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.2096</v>
+        <v>-0.1088</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2275</v>
+        <v>0.4619</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7317</v>
+        <v>0.1732</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.4341</v>
+        <v>0.7369</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7024</v>
+        <v>-0.5637</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7054</v>
+        <v>0.1799</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7756</v>
+        <v>-0.8457</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9298999999999999</v>
+        <v>1.0256</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2828</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1197</v>
+        <v>0.3622</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.101</v>
+        <v>0.6584</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0186</v>
+        <v>-0.2962</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>-1.2566</v>
       </c>
       <c r="W9" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6231</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5125</v>
+        <v>-2.6688</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7031</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8093</v>
+        <v>-1.7772</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1629</v>
+        <v>-0.189</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1788</v>
+        <v>0.9588</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0159</v>
+        <v>-1.1478</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3647</v>
+        <v>1.0829</v>
       </c>
       <c r="K10" t="n">
-        <v>2.22</v>
+        <v>1.5573</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1447</v>
+        <v>-0.4743</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2018</v>
+        <v>-1.2719</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0412</v>
+        <v>-0.5985</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1606</v>
+        <v>-0.6735</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5656</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.7647</v>
+        <v>-3.8484</v>
       </c>
       <c r="R10" t="n">
         <v>2.1991</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7878</v>
+        <v>-1.4744</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.359</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2177</v>
+        <v>-1.1154</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>0.6439</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>2.2328</v>
       </c>
       <c r="X10" t="n">
         <v>-1.5889</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.554</v>
+        <v>-2.7179</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5786</v>
+        <v>-1.0572</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9754</v>
+        <v>-1.6607</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.189</v>
+        <v>1.1629</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9588</v>
+        <v>1.1788</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1478</v>
+        <v>-0.0159</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0829</v>
+        <v>2.3647</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5573</v>
+        <v>2.22</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4743</v>
+        <v>0.1447</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2719</v>
+        <v>-1.2018</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5985</v>
+        <v>-1.0412</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6735</v>
+        <v>-0.1606</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6493</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8484</v>
+        <v>-4.7647</v>
       </c>
       <c r="R11" t="n">
         <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3596</v>
+        <v>-0.9932</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.046</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3136</v>
+        <v>-1.069</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6439</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2328</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
         <v>-1.5889</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.3406</v>
+        <v>-10.2397</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.6638</v>
+        <v>-5.5626</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6767</v>
+        <v>-4.6769</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1826</v>
+        <v>-4.182600000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-5.4646</v>
@@ -1378,7 +1378,7 @@
         <v>-6.335699999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4788000000000001</v>
+        <v>0.4788000000000002</v>
       </c>
       <c r="P12" t="n">
         <v>-3.6651</v>
@@ -1390,19 +1390,19 @@
         <v>13.7444</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.8464</v>
+        <v>-2.7452</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4414</v>
+        <v>1.5423</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.2875</v>
+        <v>-4.287599999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.3531000000000004</v>
       </c>
       <c r="W12" t="n">
-        <v>8.630199999999999</v>
+        <v>8.6302</v>
       </c>
       <c r="X12" t="n">
         <v>-8.2768</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3412</v>
+        <v>5.3501</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5181</v>
+        <v>3.5844</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8231</v>
+        <v>1.7657</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7858</v>
+        <v>4.1603</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3343</v>
+        <v>3.1986</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5484</v>
+        <v>0.9617</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2702</v>
+        <v>3.8111</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1451</v>
+        <v>3.0095</v>
       </c>
       <c r="L13" t="n">
-        <v>0.125</v>
+        <v>0.8017</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4843</v>
+        <v>0.3492</v>
       </c>
       <c r="N13" t="n">
         <v>0.1891</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6735</v>
+        <v>0.16</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.733</v>
+        <v>2.3823</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0158</v>
+        <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6549</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3975</v>
+        <v>0.0849</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2574</v>
+        <v>-0.6439</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6335</v>
+        <v>-0.6335</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5993</v>
+        <v>-0.3115</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.9658</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>P. FERRI BARCENAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6508</v>
+        <v>5.0835</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8792</v>
+        <v>3.1938</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7716</v>
+        <v>1.8897</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.151</v>
+        <v>1.8788</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1215</v>
+        <v>3.0902</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2725</v>
+        <v>-1.2114</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7744</v>
+        <v>1.5464</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4056</v>
+        <v>3.3346</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6312</v>
+        <v>-1.7882</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9253</v>
+        <v>0.3324</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.284</v>
+        <v>-0.2443</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6413</v>
+        <v>0.5768</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1991</v>
+        <v>2.7489</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9171</v>
+        <v>0.4167</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0973</v>
+        <v>0.3413</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1802</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4344</v>
+        <v>0.9554</v>
       </c>
       <c r="W14" t="n">
-        <v>4.7563</v>
+        <v>2.2224</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CASADO SEGURA</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2287</v>
+        <v>4.6814</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1043</v>
+        <v>3.6869</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1243</v>
+        <v>0.9946</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1419</v>
+        <v>-0.151</v>
       </c>
       <c r="H15" t="n">
-        <v>1.299</v>
+        <v>1.1215</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1571</v>
+        <v>-1.2725</v>
       </c>
       <c r="J15" t="n">
-        <v>0.231</v>
+        <v>0.7744</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8046</v>
+        <v>1.4056</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5736</v>
+        <v>-0.6312</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9109</v>
+        <v>-0.9253</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4944</v>
+        <v>-0.284</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4164</v>
+        <v>-0.6413</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0995</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0158</v>
+        <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5866</v>
+        <v>0.9478</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7896</v>
+        <v>0.905</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.203</v>
+        <v>0.0428</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.5993</v>
+        <v>4.4344</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.7563</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5993</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2181</v>
+        <v>3.5373</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5267</v>
+        <v>2.5566</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6914</v>
+        <v>0.9808</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1603</v>
+        <v>1.7858</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1986</v>
+        <v>2.3343</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9617</v>
+        <v>-0.5484</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8111</v>
+        <v>2.2702</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0095</v>
+        <v>2.1451</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8017</v>
+        <v>0.125</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3492</v>
+        <v>-0.4843</v>
       </c>
       <c r="N16" t="n">
         <v>0.1891</v>
       </c>
       <c r="O16" t="n">
-        <v>0.16</v>
+        <v>-0.6735</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3823</v>
+        <v>-0.733</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3823</v>
+        <v>2.0158</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.691</v>
+        <v>1.851</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9728</v>
+        <v>1.4359</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7181999999999999</v>
+        <v>0.4151</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6335</v>
+        <v>0.6335</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3115</v>
+        <v>1.5993</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3219</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. FERRI BARCENAS</t>
+          <t>J. CASADO SEGURA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.443</v>
+        <v>2.0667</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7514</v>
+        <v>0.8928</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6915</v>
+        <v>1.1739</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8788</v>
+        <v>1.1419</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0902</v>
+        <v>1.299</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2114</v>
+        <v>-0.1571</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5464</v>
+        <v>0.231</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3346</v>
+        <v>0.8046</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.7882</v>
+        <v>-0.5736</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3324</v>
+        <v>0.9109</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2443</v>
+        <v>0.4944</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5768</v>
+        <v>0.4164</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7489</v>
+        <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2238</v>
+        <v>1.4246</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.101</v>
+        <v>1.5781</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1228</v>
+        <v>-0.1535</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9554</v>
+        <v>-1.5993</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.267</v>
+        <v>-1.5993</v>
       </c>
     </row>
     <row r="18">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7604</v>
+        <v>1.0765</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0371</v>
+        <v>-0.8448</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7975</v>
+        <v>1.9213</v>
       </c>
       <c r="G19" t="n">
         <v>0.1914</v>
@@ -1936,13 +1936,13 @@
         <v>2.0158</v>
       </c>
       <c r="S19" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.3799</v>
       </c>
       <c r="T19" t="n">
-        <v>0.126</v>
+        <v>0.3183</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0622</v>
+        <v>0.0616</v>
       </c>
       <c r="V19" t="n">
         <v>0.3219</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. CORTINA CAMPOS</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3449</v>
+        <v>-0.3059</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-1.9878</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3449</v>
+        <v>1.682</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2167</v>
+        <v>0.8683</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2167</v>
+        <v>-1.4591</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.3274</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.0197</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-1.9231</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.9428</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2167</v>
+        <v>0.8486</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2167</v>
+        <v>0.464</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.3846</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1282</v>
+        <v>-0.1192</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.175</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1282</v>
+        <v>0.0558</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>X. CORTINA CAMPOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.3449</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1801</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5829</v>
+        <v>-0.3449</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8683</v>
+        <v>-0.2167</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4591</v>
+        <v>-0.2167</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3274</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0197</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9231</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9428</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8486</v>
+        <v>-0.2167</v>
       </c>
       <c r="N22" t="n">
-        <v>0.464</v>
+        <v>-0.2167</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3846</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.733</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4106</v>
+        <v>-0.1282</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3673</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0433</v>
+        <v>-0.1282</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1415</v>
+        <v>-1.089</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5756</v>
+        <v>-0.6718</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5659</v>
+        <v>-0.4173</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1013</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0299</v>
+        <v>0.0226</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2557</v>
+        <v>0.1595</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2855</v>
+        <v>-0.1369</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6439</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7083</v>
+        <v>-1.9968</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5903</v>
+        <v>-1.8787</v>
       </c>
       <c r="F24" t="n">
         <v>-0.118</v>
@@ -2326,10 +2326,10 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2195</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2006</v>
+        <v>-0.0878</v>
       </c>
       <c r="U24" t="n">
         <v>0.0188</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0218</v>
+        <v>-3.9781</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8633</v>
+        <v>-1.6709</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1585</v>
+        <v>-2.3072</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1589</v>
@@ -2404,13 +2404,13 @@
         <v>0.1833</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1353</v>
+        <v>-0.0916</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U25" t="n">
-        <v>0.195</v>
+        <v>0.0464</v>
       </c>
       <c r="V25" t="n">
         <v>-1.9109</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.7131</v>
+        <v>-4.9657</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.082</v>
+        <v>-4.409</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6311</v>
+        <v>-0.5568</v>
       </c>
       <c r="G26" t="n">
         <v>-5.3856</v>
@@ -2482,13 +2482,13 @@
         <v>1.2828</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9768</v>
+        <v>-0.2294</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8077</v>
+        <v>-0.1346</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1692</v>
+        <v>-0.0948</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6335</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>11.3409</v>
+        <v>11.3407</v>
       </c>
       <c r="E27" t="n">
-        <v>4.676899999999999</v>
+        <v>4.6771</v>
       </c>
       <c r="F27" t="n">
-        <v>6.663900000000002</v>
+        <v>6.663800000000001</v>
       </c>
       <c r="G27" t="n">
         <v>4.182500000000001</v>
@@ -2539,13 +2539,13 @@
         <v>6.335600000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4788999999999999</v>
+        <v>-0.4789000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-1.674</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.871</v>
+        <v>-0.8709999999999999</v>
       </c>
       <c r="O27" t="n">
         <v>-0.8032999999999999</v>
@@ -2563,10 +2563,10 @@
         <v>3.846200000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>4.2876</v>
+        <v>4.287600000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4413999999999999</v>
+        <v>-0.4414</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3531999999999997</v>
